--- a/artfynd/A 29994-2025 artfynd.xlsx
+++ b/artfynd/A 29994-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60629440</v>
+        <v>601827</v>
       </c>
       <c r="B2" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224416</v>
+        <v>1562</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Stortimjan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Thymus pulegioides</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bottnansmåla, Bl</t>
+          <t>Bottnansmåla SO, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537394.8372036304</v>
+        <v>537414</v>
       </c>
       <c r="R2" t="n">
-        <v>6243089.470205478</v>
+        <v>6243107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,29 +738,24 @@
           <t>Rödeby</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>K-Kna-1206</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1990-07-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1990-07-04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flera plantor.</t>
+          <t>Från "Ängar och hagar i Blekinge" (länsstyrelsens ängs- och hagmarksinventering).</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,33 +769,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>betad hagmark</t>
+          <t>hagmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>K-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
           <t>Åke Widgren</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Åke Widgren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56853214</v>
+        <v>56853212</v>
       </c>
       <c r="B3" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537428.7582137479</v>
+        <v>537429</v>
       </c>
       <c r="R3" t="n">
-        <v>6243211.72223589</v>
+        <v>6243212</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,26 +861,21 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-07-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1990-07-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-07-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1990-07-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Från länsstyrelsens Ängar och hagar i Blekinge</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -902,11 +883,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>hävdad ängsmark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -915,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kjell Pettersson</t>
+          <t>Åke Widgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -923,6 +899,223 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>60629441</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bottnansmåla, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>537414</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6243107</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rödeby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-07-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-07-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>betad hagmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>60629440</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bottnansmåla, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>537395</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6243089</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rödeby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-07-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-07-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera plantor.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>betad hagmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
